--- a/docs/xlsx/jobs-2026-08-21.xlsx
+++ b/docs/xlsx/jobs-2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="710">
   <si>
     <t>Title</t>
   </si>
@@ -274,6 +274,18 @@
     <t>https://www.conservationjobboard.com/job-listing-internship--environmental-education-naples-florida/8469650337</t>
   </si>
   <si>
+    <t>LinkedIn Specialist</t>
+  </si>
+  <si>
+    <t>The Pollination Project</t>
+  </si>
+  <si>
+    <t>$1,500 - $2,000 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-linkedin-specialist-remote-remote/8512277762</t>
+  </si>
+  <si>
     <t>Marine Science Educator</t>
   </si>
   <si>
@@ -466,15 +478,9 @@
     <t>Social Media Manager (Multiple Roles)</t>
   </si>
   <si>
-    <t>The Pollination Project</t>
-  </si>
-  <si>
     <t>remote, Remote</t>
   </si>
   <si>
-    <t>$1,500 - $2,000 per month</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-social-media-manager-multiple-roles-remote-remote/7843878207</t>
   </si>
   <si>
@@ -565,6 +571,66 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-educator-americorps-member--eastern-region-elko-nevada/7416171057</t>
   </si>
   <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Casey Trees</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/chief-financial-officer-2/</t>
+  </si>
+  <si>
+    <t>Landscape &amp; Facilities Assistant</t>
+  </si>
+  <si>
+    <t>Turner Farm Inc</t>
+  </si>
+  <si>
+    <t>Cincinnati, Ohio, United States</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Horticulture / Gardening / Landscaping</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/landscape-facilities-assistant/</t>
+  </si>
+  <si>
+    <t>Advancement Associate (Museum/Educational Institution)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 31.54 - 31.54/hour</t>
+  </si>
+  <si>
+    <t>Education, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5c7807a01c2d44ebaf831534d533dfbd-advancement-associate-museumeducational-institution-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Advocacy Manager</t>
   </si>
   <si>
@@ -595,15 +661,153 @@
     <t>Virreyes, Provincia de Buenos Aires, AR</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Children Youth, Education, Poverty</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ba001411fe334b538755e2fd0b35182f-asistente-eventos-y-campanas-para-el-equipo-de-desarrollo-de-fondos-colegio-madre-teresa-virreyes</t>
   </si>
   <si>
+    <t>Assistant Director of Strategic Communications and Content</t>
+  </si>
+  <si>
+    <t>GLBTQ Legal Advocates &amp; Defenders (GLAD Law)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dbff009aa6fb41ab95b2920980da34fa-assistant-director-of-strategic-communications-and-content-glbtq-legal-advocates-defenders-glad-law-boston</t>
+  </si>
+  <si>
+    <t>Associate Director of Anti-Violence Program</t>
+  </si>
+  <si>
+    <t>Sakhi for South Asian Survivors</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec08f16a66f04fbd9c42c81bf7743048-associate-director-of-anti-violence-program-sakhi-for-south-asian-survivors-new-york</t>
+  </si>
+  <si>
+    <t>Associate Editor, Writing for Libration</t>
+  </si>
+  <si>
+    <t>Empowerment Avenue</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 42.10 - 42.10/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1db8f26c6bbb4dadb76c55789f3e34cc-associate-editor-writing-for-libration-empowerment-avenue-oakland</t>
+  </si>
+  <si>
+    <t>AUDIENCE SERVICES GROUP SALES ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Center Theatre Group of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 24.65 - 24.65/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4e73cf53c6d4fddac6a49748eff2577-audience-services-group-sales-associate-center-theatre-group-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Billing and Collections Specialist</t>
+  </si>
+  <si>
+    <t>Upper Manhattan Mental Health Center, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec4bcc849d0f4e16a4cf9e204a2870fe-billing-and-collections-specialist-upper-manhattan-mental-health-center-inc-new-york</t>
+  </si>
+  <si>
+    <t>Blockchain Instructor</t>
+  </si>
+  <si>
+    <t>Skybil</t>
+  </si>
+  <si>
+    <t>Remote (NG)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>NGN 1000000.00/month</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/357891dbbf65485ab90b63ce31109065-blockchain-instructor-skybil-ondo</t>
+  </si>
+  <si>
+    <t>Bookkeeper</t>
+  </si>
+  <si>
+    <t>Public Defender Association of Pennsylvania</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24e2f1a10747408fba90602b0253b075-bookkeeper-public-defender-association-of-pennsylvania-philadelphia</t>
+  </si>
+  <si>
+    <t>Business Operations Manager</t>
+  </si>
+  <si>
+    <t>Smithbucklin</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c7de048d2f6a4c2d932dfdd3c8b4b8ef-business-operations-manager-smithbucklin-washington</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -613,9 +817,6 @@
     <t>Virginia Beach, Virginia</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 18720.00 - 18720.00/year</t>
   </si>
   <si>
@@ -625,6 +826,87 @@
     <t>https://www.idealist.org/en/nonprofit-job/5f1a7bb2b4f94a578dc959c517c3ddd5-case-manager-everheld-formerly-connect-with-a-wish-virginia-beach</t>
   </si>
   <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4ed90d240144ef78e2dab01639ff3fb-chief-development-officer-harlem-grown-new-york</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Oklahoma State Medical Association</t>
+  </si>
+  <si>
+    <t>Oklahoma City, Oklahoma</t>
+  </si>
+  <si>
+    <t>USD 280000.00 - 280000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/390ce61527614b32ac087ab727b436aa-chief-executive-officer-oklahoma-state-medical-association-oklahoma-city</t>
+  </si>
+  <si>
+    <t>Chief of Staff</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c6d599c5f074f7894982f671f731bc3-chief-of-staff-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Africatown Community Land Trust</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/632fd956085b425a82512678918667bc-chief-operating-officer-africatown-community-land-trust-seattle</t>
+  </si>
+  <si>
+    <t>Citywide Director – Employment Law Unit</t>
+  </si>
+  <si>
+    <t>The Legal Aid Society - New York City</t>
+  </si>
+  <si>
+    <t>USD 166000.00 - 171000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad845b0078b64f9ea13ac418898545af-citywide-director-employment-law-unit-the-legal-aid-society-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Clergy Administrative Assistant</t>
   </si>
   <si>
@@ -643,30 +925,165 @@
     <t>https://www.idealist.org/en/nonprofit-job/e12b338a5a4746b6a0f0addb7767af79-clergy-administrative-assistant-congregation-olam-tikvah-fairfax</t>
   </si>
   <si>
+    <t>Client and Office Support Specialist</t>
+  </si>
+  <si>
+    <t>Texas RioGrande Legal Aid, Inc. (TRLA)</t>
+  </si>
+  <si>
+    <t>Victoria, Texas</t>
+  </si>
+  <si>
+    <t>USD 44340.00 - 58403.96/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a80a22979f7483cb10d7b02788e9010-client-and-office-support-specialist-texas-riogrande-legal-aid-inc-trla-victoria</t>
+  </si>
+  <si>
+    <t>CLIENT AND OFFICE SUPPORT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Del Rio, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fba2e4de6b504c8facdcd168a91f3600-client-and-office-support-specialist-texas-riogrande-legal-aid-inc-trla-del-rio</t>
+  </si>
+  <si>
+    <t>Client Development Catalyst</t>
+  </si>
+  <si>
+    <t>The Non-GMO Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0d6ee51c88cb4179ae698b73824c0ca1-client-development-catalyst-the-non-gmo-project-bellingham</t>
+  </si>
+  <si>
+    <t>Clinical Manager for an Expressive Arts Practice</t>
+  </si>
+  <si>
+    <t>A Place To Be</t>
+  </si>
+  <si>
+    <t>Leesburg, Virginia</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7756e19e0fcd4d27b16485c665b32037-clinical-manager-for-an-expressive-arts-practice-a-place-to-be-leesburg</t>
+  </si>
+  <si>
+    <t>Clinical Monitor – Independent Monitoring Unit</t>
+  </si>
+  <si>
+    <t>Equip for Equality</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 60270.00 - 78950.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58b6051a6c534078bd91ef3ad79a6c69-clinical-monitor-independent-monitoring-unit-equip-for-equality-chicago</t>
+  </si>
+  <si>
     <t>Communications Manager</t>
   </si>
   <si>
     <t>Turtle Island Restoration Network</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 75000.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/50fa45a0e32d48d6af838ae87801f667-communications-manager-turtle-island-restoration-network-olema</t>
   </si>
   <si>
+    <t>Community Outreach Specialist</t>
+  </si>
+  <si>
+    <t>HopeWell Cancer Support</t>
+  </si>
+  <si>
+    <t>Timonium, Maryland</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d863d1d2aa64128816e8abd924bb0e6-community-outreach-specialist-hopewell-cancer-support-timonium</t>
+  </si>
+  <si>
+    <t>Conservation Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/995fc3a6163d49a48f9915152c6b886b-conservation-associate-environment-america-richmond</t>
+  </si>
+  <si>
+    <t>Consultoría para la identificación y atracción de stakeholders y pagadores de resultados para los pilotos de Pago por Resultados</t>
+  </si>
+  <si>
+    <t>Alterna Impact</t>
+  </si>
+  <si>
+    <t>Guatemala City, Ciudad de Guatemala, GT</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/615d1d59bdca40b78c1a3d03f802f966-consultoria-para-la-identificacion-y-atraccion-de-stakeholders-y-pagadores-de-resultados-para-los-pilotos-de-pago-por-resultados-alterna-impact-guatemala-city</t>
+  </si>
+  <si>
+    <t>Contract Management Associate III</t>
+  </si>
+  <si>
+    <t>Fresh Lifelines for Youth</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 30.29 - 30.29/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7686e01440a0477d888ff2bbcaa01429-contract-management-associate-iii-fresh-lifelines-for-youth-san-jose</t>
+  </si>
+  <si>
     <t>Coordinator, Donor Acknowledgements New York</t>
   </si>
   <si>
     <t>AJC</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 50000.00 - 55000.00/year</t>
   </si>
   <si>
@@ -691,15 +1108,204 @@
     <t>https://www.idealist.org/en/nonprofit-job/2991f65e107c40bc8e68a4f2be30c135-coordinator-population-health-initiatives-health-equity-amga-american-medical-group-association-alexandria</t>
   </si>
   <si>
+    <t>Coordinator, Programs</t>
+  </si>
+  <si>
+    <t>LINK Unlimited Scholars</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 53000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b82a0b9bd7b54079b610b2cc73cafed1-coordinator-programs-link-unlimited-scholars-chicago</t>
+  </si>
+  <si>
+    <t>Deputy Director, Social Media</t>
+  </si>
+  <si>
+    <t>USD 109500.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2eda3f47c05f4b4ca27c87eac119b9f5-deputy-director-social-media-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Development &amp; Operations Associate</t>
+  </si>
+  <si>
+    <t>Northwest Abortion Access Fund</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 36.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cd27856d40664706845a1d4d21e0f9b8-development-operations-associate-northwest-abortion-access-fund-portland</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/25d359f5f0d34175b1bc906d81e75218-development-assistant-careers-in-nonprofits-inc-washington</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Parking Reform Network</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Transportation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6d3098a1f1f4fc7b2a924fc1796b04e-development-manager-parking-reform-network-portland</t>
+  </si>
+  <si>
+    <t>DevOps Engineering Instructor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/community-job/732bcb26a82f4a238831a05340a03cd2-devops-engineering-instructor-skybil-ondo</t>
+  </si>
+  <si>
+    <t>Digital Fundraising Coordinator</t>
+  </si>
+  <si>
+    <t>Citizens for Responsibility and Ethics in Washington</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1bde840472c4b14bb89d7cfcec0ab0f-digital-fundraising-coordinator-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Direct Mail Specialist - Entry Level</t>
+  </si>
+  <si>
+    <t>Sanky Communications, Inc.</t>
+  </si>
+  <si>
+    <t>USD 44600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/87cdedcee5b24847a263016bab47a86d-direct-mail-specialist-entry-level-sanky-communications-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b99b5f0915724570b8707143ab91ac93-director-of-communications-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Sports &amp; Fitness</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2cd2502c88f462b97cc72decee58dae-director-of-sports-fitness-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Director, Communications &amp; Writing</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ee39ef14427408581855798b0273c32-director-communications-writing-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the President</t>
+  </si>
+  <si>
+    <t>National Center for LGBTQ Rights</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ea9c2e6514145a0953d010ec21b2b81-executive-assistant-to-the-president-national-center-for-lgbtq-rights-san-francisco</t>
+  </si>
+  <si>
+    <t>Las Vegas New Mexico Community Foundation</t>
+  </si>
+  <si>
+    <t>Las Vegas, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc5506be669f40f5abcdc61e44a6266b-executive-director-las-vegas-new-mexico-community-foundation-las-vegas</t>
+  </si>
+  <si>
+    <t>Executive Director Cake4Kids</t>
+  </si>
+  <si>
+    <t>Cake4Kids</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7a0050e39e54d778c59f90edd5826f1-executive-director-cake4kids-cake4kids-sunnyvale</t>
+  </si>
+  <si>
     <t>Extractive Industries Campaign Lead</t>
   </si>
   <si>
     <t>Environmental Investigation Agency - Washington, DC</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 107000.00 - 122000.00/year</t>
   </si>
   <si>
@@ -727,15 +1333,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/e1b93cee5ac6498eab5d3133c5c978c5-family-defense-program-director-americans-for-immigrant-justice-miami</t>
   </si>
   <si>
+    <t>Farm Manager – Food for Change Hydroponic Program</t>
+  </si>
+  <si>
+    <t>Center for Food As Medicine</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Agriculture, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9df8f92ecf714c279c95a91c1378f544-farm-manager-food-for-change-hydroponic-program-center-for-food-as-medicine-new-york</t>
+  </si>
+  <si>
     <t>Freelancer season Fundraiser</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 50.00 - 100.00/month</t>
   </si>
   <si>
@@ -745,15 +1363,84 @@
     <t>https://www.idealist.org/en/nonprofit-job/bdf10da91cf94c26a6b70d18bdf41b7f-freelancer-season-fundraiser-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>La Casa de Maria</t>
+  </si>
+  <si>
+    <t>Montecito, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb714703550e41f68faa5484cb336538-general-manager-la-casa-de-maria-montecito</t>
+  </si>
+  <si>
+    <t>Global Communications Senior Manager/Director</t>
+  </si>
+  <si>
+    <t>IMPACT Transforming Natural Resource Management</t>
+  </si>
+  <si>
+    <t>Remote (Ottawa, Ontario, CA)</t>
+  </si>
+  <si>
+    <t>CAD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Conflict Resolution, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/858b5a331c934115abc1e463aed9ffec-global-communications-senior-managerdirector-impact-transforming-natural-resource-management-ottawa</t>
+  </si>
+  <si>
+    <t>Remote (Montreal, Quebec, CA)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/400ff6b7ef374811b55ba0470d6d7df4-global-communications-senior-managerdirector-impact-transforming-natural-resource-management-montreal</t>
+  </si>
+  <si>
+    <t>Grant Accountant</t>
+  </si>
+  <si>
+    <t>Legal Services of Northern California</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 5113.00 - 7225.00/month</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1f1073c121344f5b046123b3f415a7f-grant-accountant-legal-services-of-northern-california-sacramento</t>
+  </si>
+  <si>
+    <t>Grants Associate</t>
+  </si>
+  <si>
+    <t>Fauna &amp; Flora International</t>
+  </si>
+  <si>
+    <t>USD 61045.00 - 61045.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9680482a4db4dcf8707082167824c62-grants-associate-fauna-flora-international-cambridge</t>
+  </si>
+  <si>
     <t>High School Squash Coordinator</t>
   </si>
   <si>
     <t>MetroSquash</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 40000.00 - 50000.00/year</t>
   </si>
   <si>
@@ -763,6 +1450,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/7365d07751af4713adfd39ff6bc502fd-high-school-squash-coordinator-metrosquash-chicago</t>
   </si>
   <si>
+    <t>Housing and Benefit Attorney, Civil Justice Practice</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 184000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16d5ca92e4a64a9b8e16d0dc7859b9e6-housing-and-benefit-attorney-civil-justice-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Human Resources Organization Partner</t>
+  </si>
+  <si>
+    <t>Service Employees International Union - SEIU</t>
+  </si>
+  <si>
+    <t>USD 108104.00 - 108105.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4287775501c84e39a5d45a5ce599955a-human-resources-organization-partner-service-employees-international-union-seiu-washington</t>
+  </si>
+  <si>
     <t>Individual Giving Manager</t>
   </si>
   <si>
@@ -778,6 +1495,114 @@
     <t>https://www.idealist.org/en/nonprofit-job/cf0b94aa275c41c2a265670a92bacd26-individual-giving-manager-chicago-abortion-fund-chicago</t>
   </si>
   <si>
+    <t>Institutional Giving Manager</t>
+  </si>
+  <si>
+    <t>Greater DC Diaper Bank</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d02bc7818894895b3ede0f796e3e846-institutional-giving-manager-greater-dc-diaper-bank-silver-spring</t>
+  </si>
+  <si>
+    <t>Law Reform &amp; Policy Paralegal</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8366cad0873541b4a8e303779a328837-law-reform-policy-paralegal-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Manager, Grants and Operations</t>
+  </si>
+  <si>
+    <t>IntermediaryEd</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 100400.00 - 119400.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2082a19ae6cd423ea2ef19b8b8d52ff9-manager-grants-and-operations-intermediaryed-newark</t>
+  </si>
+  <si>
+    <t>Manager, Grants Controlling</t>
+  </si>
+  <si>
+    <t>Regulatory Assistance Project</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd6f93644733485b9851543e5d8b32e2-manager-grants-controlling-regulatory-assistance-project-montpelier</t>
+  </si>
+  <si>
+    <t>Manager, Total Rewards</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Community Development, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db8db4503c924b17960bd46d50667b37-manager-total-rewards-upper-manhattan-mental-health-center-inc-new-york</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Kultivate Labs</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 70304.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aaaf400e200c44588fc528b45c3a10cc-marketing-programs-coordinator-kultivate-labs-san-francisco</t>
+  </si>
+  <si>
+    <t>New York Program Associate</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b86164f3fe6a481dba8f1da7fd191e75-new-york-program-associate-american-farmland-trust-saratoga-springs</t>
+  </si>
+  <si>
+    <t>Ocean Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff69e2d54fd4421aba02407ab5194203-ocean-associate-environment-america-boston</t>
+  </si>
+  <si>
     <t>Operations Associate</t>
   </si>
   <si>
@@ -793,15 +1618,129 @@
     <t>https://www.idealist.org/en/nonprofit-job/a3a9c329946a4b3aa1b3f036354dabe1-operations-associate-cities-for-financial-empowerment-fund-new-york</t>
   </si>
   <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Kinship House</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b0e1982cb3a49d8beba600b6dc1bb50-operations-coordinator-kinship-house-portland</t>
+  </si>
+  <si>
+    <t>Outpatient Clinician/ Therapist</t>
+  </si>
+  <si>
+    <t>New Alternatives, Inc.</t>
+  </si>
+  <si>
+    <t>Chula Vista, California</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e73315a364b435fac598c23f845ad75-outpatient-clinician-therapist-new-alternatives-inc-chula-vista</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>1199SEIU Funds</t>
+  </si>
+  <si>
+    <t>USD 57800.00 - 72300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afb882004a514bbd81ced7ce0537fd7f-paralegal-1199seiu-funds-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal B</t>
+  </si>
+  <si>
+    <t>Laredo, Texas</t>
+  </si>
+  <si>
+    <t>USD 45340.00 - 59501.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac8a1ee816a24df494f90be84cb52459-paralegal-b-texas-riogrande-legal-aid-inc-trla-laredo</t>
+  </si>
+  <si>
+    <t>Payroll and Benefits Specilaist</t>
+  </si>
+  <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d1e19595fdd4c62a567aa5751806f54-payroll-and-benefits-specilaist-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>People Operations Associate</t>
+  </si>
+  <si>
+    <t>Hudson Guild</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b161f723300450a9169a1dfdcceef5c-people-operations-associate-hudson-guild-new-york</t>
+  </si>
+  <si>
+    <t>Policy Director</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>USD 143147.00 - 170925.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05d05d96473a4080b5aa0bc548a9b1f8-policy-director-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Posse Scholarship Hired Interviewer</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Los Angeles</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 18.42 - 18.42/hour</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/439639ce37a04e05b8849b957d6624af-posse-scholarship-hired-interviewer-the-posse-foundation-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Prison and Reentry Program Manager</t>
   </si>
   <si>
     <t>Defy Ventures</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 32.69 - 34.13/hour</t>
   </si>
   <si>
@@ -811,6 +1750,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/cb4a4aa6590b4c069082a3acb314342c-prison-and-reentry-program-manager-defy-ventures-seattle</t>
   </si>
   <si>
+    <t>Prison and Reentry Program Manager, Defy Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb4a4aa6590b4c069082a3acb314342c-prison-and-reentry-program-manager-defy-washington-defy-ventures-seattle</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Vision To Learn</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9aba910d4e84c9bac7dd8e61b2cb10e-program-coordinator-vision-to-learn-madison</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>USD 58500.00 - 58500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8aba1dc79564431fac9cca8f122f7e92-program-director-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d88b73907324ff39b1b18643bf06b57-program-manager-vision-to-learn-columbus</t>
+  </si>
+  <si>
     <t>Program Manager - Nigeria</t>
   </si>
   <si>
@@ -829,6 +1813,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/0c44bbdd711e4ba39df0cf292ec32e87-program-manager-nigeria-intersos-maiduguri</t>
   </si>
   <si>
+    <t>Registered Nurse</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49ae086ba0b44d77bdf4be3d85acbbbf-registered-nurse-upper-manhattan-mental-health-center-inc-new-york</t>
+  </si>
+  <si>
+    <t>Restorative Practices Youth Training Specialist 1</t>
+  </si>
+  <si>
+    <t>Build 2 Lead</t>
+  </si>
+  <si>
+    <t>Federal Way, Washington</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f68d18a5e674324b04470ee1a921c8f-restorative-practices-youth-training-specialist-1-build-2-lead-federal-way</t>
+  </si>
+  <si>
+    <t>Senior Manager, Campaign Research</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/268bbc6d822d4dcca0cd2c72018a537f-senior-manager-campaign-research-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Leadership Counsel for Justice and Accountability</t>
+  </si>
+  <si>
+    <t>Fresno, California</t>
+  </si>
+  <si>
+    <t>USD 89500.00 - 117500.00/year</t>
+  </si>
+  <si>
+    <t>Rural Areas, Climate Change, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fee24e4328244e2c97a4e0f7b380fd04-senior-staff-attorney-leadership-counsel-for-justice-and-accountability-fresno</t>
+  </si>
+  <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>USD 113500.00 - 113501.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ff66e7b6eccd4eb691d0e565077b73c9-senior-staff-attorney-new-york-civil-liberties-union-foundation-new-york</t>
+  </si>
+  <si>
     <t>Social Work Supervisor, Bronx</t>
   </si>
   <si>
@@ -841,10 +1888,262 @@
     <t>USD 91500.00 - 120636.28/year</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/ef2bad24990d4fe2ae1c87875fb34630-social-work-supervisor-bronx-the-childrens-law-center-ny-bronx</t>
+  </si>
+  <si>
+    <t>SONYC - COMPASS Group Leader (BCS)</t>
+  </si>
+  <si>
+    <t>Inspiring Minds NYC</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21ec459be45544f7bf0430f795821eba-sonyc-compass-group-leader-bcs-inspiring-minds-nyc-kings-county</t>
+  </si>
+  <si>
+    <t>SONYC - COMPASS Program Director (BCS)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68e5ebc2d0a241689566b906931adf4e-sonyc-compass-program-director-bcs-inspiring-minds-nyc-kings-county</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Civil Survival Project</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 85579.99 - 129447.42/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd0401c1baf34e428f14082406f91060-staff-attorney-civil-survival-project-port-orchard</t>
+  </si>
+  <si>
+    <t>Philadelphia VIP</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 64450.00 - 69450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6093cd0ace04c6a8aa6877d4fa7f9c3-staff-attorney-philadelphia-vip-philadelphia</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Homelessness Prevention (Affirmative Litigation)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9173ac9a77424fddae33e8c8a7e0db92-staff-attorney-homelessness-prevention-affirmative-litigation-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Bronx</t>
+  </si>
+  <si>
+    <t>USD 86700.00 - 140472.21/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/984b90dfcd984a8b9731143a27ff6e18-staff-attorney-bronx-the-childrens-law-center-ny-bronx</t>
+  </si>
+  <si>
+    <t>State Affairs Counsel</t>
+  </si>
+  <si>
+    <t>American Association for Justice</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/980352c807f74bbb9997fc87c186ab23-state-affairs-counsel-american-association-for-justice-washington</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbc211d526114b099fe491d5f4d12bd4-supervising-attorney-philadelphia-vip-philadelphia</t>
+  </si>
+  <si>
+    <t>Supervising Immigration Attorney</t>
+  </si>
+  <si>
+    <t>International Institute of Buffalo</t>
+  </si>
+  <si>
+    <t>Buffalo, NY</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c531c22e6a847e381589be3d864fae5-supervising-immigration-attorney-international-institute-of-buffalo-buffalo</t>
+  </si>
+  <si>
+    <t>Support Group Facilitator</t>
+  </si>
+  <si>
+    <t>USD 250.00 - 250.00/week</t>
+  </si>
+  <si>
+    <t>Health Medicine, Men, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dab9146a008f4f078e489b8a0f2880e8-support-group-facilitator-hopewell-cancer-support-timonium</t>
+  </si>
+  <si>
+    <t>Technology Director</t>
+  </si>
+  <si>
+    <t>Center for Constitutional Rights</t>
+  </si>
+  <si>
+    <t>USD 138332.00 - 188591.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/85f414fcb1fd4055893ae850aafd5c54-technology-director-center-for-constitutional-rights-new-york</t>
+  </si>
+  <si>
+    <t>Teen Coordinator</t>
+  </si>
+  <si>
+    <t>BOYS &amp; GIRLS CLUB OF MARSHFIELD INC</t>
+  </si>
+  <si>
+    <t>MARSHFIELD, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55d1f44f5be94d319499f33196fe8e28-teen-coordinator-boys-girls-club-of-marshfield-inc-marshfield</t>
+  </si>
+  <si>
+    <t>Tenant Rights Program Lead</t>
+  </si>
+  <si>
+    <t>Inquilinos Unidos (United Tenants)</t>
+  </si>
+  <si>
+    <t>USD 36.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Urban Areas, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c9874dc2abc4a62bcef3cd5abac8fdb-tenant-rights-program-lead-inquilinos-unidos-united-tenants-los-angeles</t>
+  </si>
+  <si>
+    <t>Toddler Teacher - Seola Gardens</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>USD 26.18 - 29.05/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/655253d16f1a47a38179fe83b0e90fc9-toddler-teacher-seola-gardens-neighborhood-house-seattle</t>
+  </si>
+  <si>
+    <t>Union Square Greenmarket Operations Coordinator</t>
+  </si>
+  <si>
+    <t>GrowNYC</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95bf77e910bf4df0b7a7027770f0ff6b-union-square-greenmarket-operations-coordinator-grownyc-new-york</t>
+  </si>
+  <si>
+    <t>Urban Forestry Crew Leader Trainee</t>
+  </si>
+  <si>
+    <t>Elderberry Wisdom Farm</t>
+  </si>
+  <si>
+    <t>Salem, Oregon</t>
+  </si>
+  <si>
+    <t>USD 1555.00 - 1555.00/month</t>
+  </si>
+  <si>
+    <t>Education, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d71fe27416d44d9fb8ec416dbd80db23-urban-forestry-crew-leader-trainee-elderberry-wisdom-farm-salem</t>
+  </si>
+  <si>
+    <t>Voter Registration Field Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44474.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebb876b10eb2476f98409d91903aeeea-voter-registration-field-organizer-student-pirgs-tampa</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90249888cde641b79efc2c8b485506af-voter-registration-field-organizer-student-pirgs-madison</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d6d9d2b61e34433afa3268071e12895-voter-registration-field-organizer-student-pirgs-atlanta</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/283a0a0fd16940ac9730a10f1fdea2eb-voter-registration-field-organizer-student-pirgs-philadelphia</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1631b36b48fa47f8b09febad5a43a6db-voter-registration-field-organizer-student-pirgs-austin</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1576,387 +2875,410 @@
         <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
         <v>92</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
         <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
         <v>103</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>104</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>109</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F19" t="s">
-        <v>112</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
         <v>114</v>
-      </c>
-      <c r="B20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
         <v>120</v>
-      </c>
-      <c r="B21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F21" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
         <v>126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F22" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
         <v>132</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
         <v>133</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>134</v>
       </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="H23" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
         <v>137</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>138</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
         <v>139</v>
       </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F24" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
         <v>143</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
         <v>144</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>145</v>
       </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="H25" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F25" t="s">
-        <v>147</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" t="s">
         <v>149</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
         <v>150</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
         <v>151</v>
       </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="H26" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
         <v>154</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C27" t="s">
-        <v>156</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>157</v>
-      </c>
-      <c r="F27" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F28" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" t="s">
         <v>165</v>
       </c>
-      <c r="B29" t="s">
+      <c r="H29" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C29" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>168</v>
-      </c>
-      <c r="F29" t="s">
-        <v>169</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>176</v>
+      </c>
+      <c r="F31" t="s">
         <v>177</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H31" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>179</v>
       </c>
-      <c r="D31" t="s">
+      <c r="B32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" t="s">
         <v>18</v>
       </c>
-      <c r="E31" t="s">
-        <v>180</v>
-      </c>
-      <c r="F31" t="s">
-        <v>181</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="E32" t="s">
         <v>182</v>
+      </c>
+      <c r="F32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1992,6 +3314,7 @@
     <hyperlink ref="H29" r:id="rId28"/>
     <hyperlink ref="H30" r:id="rId29"/>
     <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2000,7 +3323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2039,8 +3362,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2048,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2089,370 +3462,2463 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="F3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="F8" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E9" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>251</v>
       </c>
       <c r="E10" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F10" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="F12" t="s">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="F13" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="F14" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E15" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="F15" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="F16" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="F17" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>292</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" t="s">
+        <v>294</v>
+      </c>
+      <c r="F18" t="s">
+        <v>295</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D19" t="s">
+        <v>208</v>
+      </c>
+      <c r="E19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" t="s">
+        <v>301</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" t="s">
+        <v>306</v>
+      </c>
+      <c r="F20" t="s">
+        <v>307</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" t="s">
+        <v>306</v>
+      </c>
+      <c r="F21" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" t="s">
+        <v>195</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D23" t="s">
+        <v>208</v>
+      </c>
+      <c r="E23" t="s">
+        <v>318</v>
+      </c>
+      <c r="F23" t="s">
+        <v>319</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" t="s">
+        <v>322</v>
+      </c>
+      <c r="C24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D24" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" t="s">
+        <v>324</v>
+      </c>
+      <c r="F24" t="s">
+        <v>325</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" t="s">
+        <v>328</v>
+      </c>
+      <c r="C25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" t="s">
+        <v>329</v>
+      </c>
+      <c r="F25" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B26" t="s">
+        <v>332</v>
+      </c>
+      <c r="C26" t="s">
+        <v>333</v>
+      </c>
+      <c r="D26" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26" t="s">
+        <v>334</v>
+      </c>
+      <c r="F26" t="s">
+        <v>335</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>337</v>
+      </c>
+      <c r="B27" t="s">
+        <v>338</v>
+      </c>
+      <c r="C27" t="s">
+        <v>339</v>
+      </c>
+      <c r="D27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" t="s">
+        <v>340</v>
+      </c>
+      <c r="F27" t="s">
+        <v>341</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B28" t="s">
+        <v>344</v>
+      </c>
+      <c r="C28" t="s">
+        <v>345</v>
+      </c>
+      <c r="D28" t="s">
+        <v>208</v>
+      </c>
+      <c r="E28" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" t="s">
+        <v>346</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>348</v>
+      </c>
+      <c r="B29" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" t="s">
+        <v>350</v>
+      </c>
+      <c r="D29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" t="s">
+        <v>352</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>354</v>
+      </c>
+      <c r="B30" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" t="s">
+        <v>356</v>
+      </c>
+      <c r="F30" t="s">
+        <v>357</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>359</v>
+      </c>
+      <c r="B31" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31" t="s">
+        <v>231</v>
+      </c>
+      <c r="D31" t="s">
+        <v>208</v>
+      </c>
+      <c r="E31" t="s">
+        <v>361</v>
+      </c>
+      <c r="F31" t="s">
+        <v>362</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>364</v>
+      </c>
+      <c r="B32" t="s">
+        <v>365</v>
+      </c>
+      <c r="C32" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" t="s">
+        <v>208</v>
+      </c>
+      <c r="E32" t="s">
+        <v>366</v>
+      </c>
+      <c r="F32" t="s">
+        <v>367</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>369</v>
+      </c>
+      <c r="B33" t="s">
+        <v>281</v>
+      </c>
+      <c r="C33" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" t="s">
+        <v>370</v>
+      </c>
+      <c r="F33" t="s">
+        <v>284</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>372</v>
+      </c>
+      <c r="B34" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" t="s">
+        <v>374</v>
+      </c>
+      <c r="D34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" t="s">
+        <v>375</v>
+      </c>
+      <c r="F34" t="s">
+        <v>376</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" t="s">
+        <v>379</v>
+      </c>
+      <c r="C35" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" t="s">
+        <v>380</v>
+      </c>
+      <c r="F35" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" t="s">
+        <v>384</v>
+      </c>
+      <c r="F36" t="s">
+        <v>385</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" t="s">
+        <v>250</v>
+      </c>
+      <c r="D37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E37" t="s">
+        <v>252</v>
+      </c>
+      <c r="F37" t="s">
+        <v>253</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>389</v>
+      </c>
+      <c r="B38" t="s">
+        <v>390</v>
+      </c>
+      <c r="C38" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" t="s">
+        <v>391</v>
+      </c>
+      <c r="F38" t="s">
+        <v>392</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>394</v>
+      </c>
+      <c r="B39" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" t="s">
+        <v>208</v>
+      </c>
+      <c r="E39" t="s">
+        <v>396</v>
+      </c>
+      <c r="F39" t="s">
+        <v>195</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>398</v>
+      </c>
+      <c r="B40" t="s">
+        <v>399</v>
+      </c>
+      <c r="C40" t="s">
+        <v>400</v>
+      </c>
+      <c r="D40" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" t="s">
+        <v>401</v>
+      </c>
+      <c r="F40" t="s">
+        <v>402</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>404</v>
+      </c>
+      <c r="B41" t="s">
+        <v>405</v>
+      </c>
+      <c r="C41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" t="s">
+        <v>406</v>
+      </c>
+      <c r="F41" t="s">
+        <v>407</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>409</v>
+      </c>
+      <c r="B42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" t="s">
+        <v>282</v>
+      </c>
+      <c r="D42" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" t="s">
+        <v>370</v>
+      </c>
+      <c r="F42" t="s">
+        <v>284</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>411</v>
+      </c>
+      <c r="B43" t="s">
+        <v>412</v>
+      </c>
+      <c r="C43" t="s">
+        <v>413</v>
+      </c>
+      <c r="D43" t="s">
+        <v>208</v>
+      </c>
+      <c r="E43" t="s">
+        <v>414</v>
+      </c>
+      <c r="F43" t="s">
+        <v>415</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>417</v>
+      </c>
+      <c r="C44" t="s">
+        <v>418</v>
+      </c>
+      <c r="D44" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" t="s">
+        <v>419</v>
+      </c>
+      <c r="F44" t="s">
+        <v>420</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>422</v>
+      </c>
+      <c r="B45" t="s">
+        <v>423</v>
+      </c>
+      <c r="C45" t="s">
+        <v>424</v>
+      </c>
+      <c r="D45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" t="s">
+        <v>425</v>
+      </c>
+      <c r="F45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>428</v>
+      </c>
+      <c r="B46" t="s">
+        <v>429</v>
+      </c>
+      <c r="C46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" t="s">
+        <v>430</v>
+      </c>
+      <c r="F46" t="s">
+        <v>431</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>433</v>
+      </c>
+      <c r="B47" t="s">
+        <v>434</v>
+      </c>
+      <c r="C47" t="s">
+        <v>435</v>
+      </c>
+      <c r="D47" t="s">
+        <v>208</v>
+      </c>
+      <c r="E47" t="s">
+        <v>436</v>
+      </c>
+      <c r="F47" t="s">
+        <v>437</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" t="s">
+        <v>440</v>
+      </c>
+      <c r="C48" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" t="s">
+        <v>208</v>
+      </c>
+      <c r="E48" t="s">
+        <v>441</v>
+      </c>
+      <c r="F48" t="s">
+        <v>442</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>444</v>
+      </c>
+      <c r="B49" t="s">
+        <v>445</v>
+      </c>
+      <c r="C49" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" t="s">
+        <v>446</v>
+      </c>
+      <c r="F49" t="s">
+        <v>447</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>449</v>
+      </c>
+      <c r="B50" t="s">
+        <v>450</v>
+      </c>
+      <c r="C50" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" t="s">
+        <v>452</v>
+      </c>
+      <c r="F50" t="s">
+        <v>453</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>455</v>
+      </c>
+      <c r="B51" t="s">
+        <v>456</v>
+      </c>
+      <c r="C51" t="s">
+        <v>457</v>
+      </c>
+      <c r="D51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E51" t="s">
+        <v>458</v>
+      </c>
+      <c r="F51" t="s">
+        <v>459</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" t="s">
+        <v>456</v>
+      </c>
+      <c r="C52" t="s">
+        <v>461</v>
+      </c>
+      <c r="D52" t="s">
+        <v>208</v>
+      </c>
+      <c r="E52" t="s">
+        <v>458</v>
+      </c>
+      <c r="F52" t="s">
+        <v>459</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>463</v>
+      </c>
+      <c r="B53" t="s">
+        <v>464</v>
+      </c>
+      <c r="C53" t="s">
+        <v>465</v>
+      </c>
+      <c r="D53" t="s">
+        <v>208</v>
+      </c>
+      <c r="E53" t="s">
+        <v>466</v>
+      </c>
+      <c r="F53" t="s">
+        <v>467</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>469</v>
+      </c>
+      <c r="B54" t="s">
+        <v>470</v>
+      </c>
+      <c r="C54" t="s">
+        <v>231</v>
+      </c>
+      <c r="D54" t="s">
+        <v>208</v>
+      </c>
+      <c r="E54" t="s">
+        <v>471</v>
+      </c>
+      <c r="F54" t="s">
+        <v>341</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>473</v>
+      </c>
+      <c r="B55" t="s">
+        <v>474</v>
+      </c>
+      <c r="C55" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" t="s">
+        <v>208</v>
+      </c>
+      <c r="E55" t="s">
+        <v>475</v>
+      </c>
+      <c r="F55" t="s">
+        <v>476</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>478</v>
+      </c>
+      <c r="B56" t="s">
+        <v>479</v>
+      </c>
+      <c r="C56" t="s">
+        <v>480</v>
+      </c>
+      <c r="D56" t="s">
+        <v>208</v>
+      </c>
+      <c r="E56" t="s">
+        <v>481</v>
+      </c>
+      <c r="F56" t="s">
+        <v>482</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>484</v>
+      </c>
+      <c r="B57" t="s">
+        <v>485</v>
+      </c>
+      <c r="C57" t="s">
+        <v>200</v>
+      </c>
+      <c r="D57" t="s">
+        <v>208</v>
+      </c>
+      <c r="E57" t="s">
+        <v>486</v>
+      </c>
+      <c r="F57" t="s">
+        <v>195</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>488</v>
+      </c>
+      <c r="B58" t="s">
+        <v>489</v>
+      </c>
+      <c r="C58" t="s">
+        <v>323</v>
+      </c>
+      <c r="D58" t="s">
+        <v>208</v>
+      </c>
+      <c r="E58" t="s">
+        <v>490</v>
+      </c>
+      <c r="F58" t="s">
+        <v>491</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>493</v>
+      </c>
+      <c r="B59" t="s">
+        <v>494</v>
+      </c>
+      <c r="C59" t="s">
+        <v>495</v>
+      </c>
+      <c r="D59" t="s">
+        <v>208</v>
+      </c>
+      <c r="E59" t="s">
+        <v>496</v>
+      </c>
+      <c r="F59" t="s">
+        <v>497</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>479</v>
+      </c>
+      <c r="C60" t="s">
+        <v>480</v>
+      </c>
+      <c r="D60" t="s">
+        <v>208</v>
+      </c>
+      <c r="E60" t="s">
+        <v>500</v>
+      </c>
+      <c r="F60" t="s">
+        <v>482</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>502</v>
+      </c>
+      <c r="B61" t="s">
+        <v>503</v>
+      </c>
+      <c r="C61" t="s">
+        <v>504</v>
+      </c>
+      <c r="D61" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" t="s">
+        <v>505</v>
+      </c>
+      <c r="F61" t="s">
+        <v>506</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>508</v>
+      </c>
+      <c r="B62" t="s">
+        <v>509</v>
+      </c>
+      <c r="C62" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" t="s">
+        <v>208</v>
+      </c>
+      <c r="E62" t="s">
+        <v>510</v>
+      </c>
+      <c r="F62" t="s">
+        <v>511</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>513</v>
+      </c>
+      <c r="B63" t="s">
+        <v>243</v>
+      </c>
+      <c r="C63" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" t="s">
+        <v>208</v>
+      </c>
+      <c r="E63" t="s">
+        <v>514</v>
+      </c>
+      <c r="F63" t="s">
+        <v>515</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>517</v>
+      </c>
+      <c r="B64" t="s">
+        <v>518</v>
+      </c>
+      <c r="C64" t="s">
+        <v>413</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" t="s">
+        <v>519</v>
+      </c>
+      <c r="F64" t="s">
+        <v>520</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>522</v>
+      </c>
+      <c r="B65" t="s">
+        <v>523</v>
+      </c>
+      <c r="C65" t="s">
+        <v>524</v>
+      </c>
+      <c r="D65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" t="s">
+        <v>525</v>
+      </c>
+      <c r="F65" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>527</v>
+      </c>
+      <c r="B66" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" t="s">
+        <v>208</v>
+      </c>
+      <c r="E66" t="s">
+        <v>340</v>
+      </c>
+      <c r="F66" t="s">
+        <v>341</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>529</v>
+      </c>
+      <c r="B67" t="s">
+        <v>530</v>
+      </c>
+      <c r="C67" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" t="s">
+        <v>208</v>
+      </c>
+      <c r="E67" t="s">
+        <v>531</v>
+      </c>
+      <c r="F67" t="s">
+        <v>532</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>534</v>
+      </c>
+      <c r="B68" t="s">
+        <v>535</v>
+      </c>
+      <c r="C68" t="s">
+        <v>374</v>
+      </c>
+      <c r="D68" t="s">
+        <v>208</v>
+      </c>
+      <c r="E68" t="s">
+        <v>380</v>
+      </c>
+      <c r="F68" t="s">
+        <v>536</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>538</v>
+      </c>
+      <c r="B69" t="s">
+        <v>539</v>
+      </c>
+      <c r="C69" t="s">
+        <v>540</v>
+      </c>
+      <c r="D69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E69" t="s">
+        <v>541</v>
+      </c>
+      <c r="F69" t="s">
+        <v>542</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>544</v>
+      </c>
+      <c r="B70" t="s">
+        <v>545</v>
+      </c>
+      <c r="C70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" t="s">
+        <v>208</v>
+      </c>
+      <c r="E70" t="s">
+        <v>546</v>
+      </c>
+      <c r="F70" t="s">
+        <v>402</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>548</v>
+      </c>
+      <c r="B71" t="s">
+        <v>304</v>
+      </c>
+      <c r="C71" t="s">
+        <v>549</v>
+      </c>
+      <c r="D71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E71" t="s">
+        <v>550</v>
+      </c>
+      <c r="F71" t="s">
+        <v>307</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>552</v>
+      </c>
+      <c r="B72" t="s">
+        <v>553</v>
+      </c>
+      <c r="C72" t="s">
+        <v>413</v>
+      </c>
+      <c r="D72" t="s">
+        <v>208</v>
+      </c>
+      <c r="E72" t="s">
+        <v>554</v>
+      </c>
+      <c r="F72" t="s">
+        <v>555</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>557</v>
+      </c>
+      <c r="B73" t="s">
+        <v>558</v>
+      </c>
+      <c r="C73" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" t="s">
+        <v>208</v>
+      </c>
+      <c r="E73" t="s">
+        <v>559</v>
+      </c>
+      <c r="F73" t="s">
+        <v>560</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>562</v>
+      </c>
+      <c r="B74" t="s">
+        <v>563</v>
+      </c>
+      <c r="C74" t="s">
+        <v>413</v>
+      </c>
+      <c r="D74" t="s">
+        <v>208</v>
+      </c>
+      <c r="E74" t="s">
+        <v>564</v>
+      </c>
+      <c r="F74" t="s">
+        <v>565</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>567</v>
+      </c>
+      <c r="B75" t="s">
+        <v>568</v>
+      </c>
+      <c r="C75" t="s">
+        <v>400</v>
+      </c>
+      <c r="D75" t="s">
+        <v>569</v>
+      </c>
+      <c r="E75" t="s">
+        <v>570</v>
+      </c>
+      <c r="F75" t="s">
+        <v>571</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>573</v>
+      </c>
+      <c r="B76" t="s">
+        <v>574</v>
+      </c>
+      <c r="C76" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" t="s">
+        <v>575</v>
+      </c>
+      <c r="F76" t="s">
+        <v>576</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>578</v>
+      </c>
+      <c r="B77" t="s">
+        <v>574</v>
+      </c>
+      <c r="C77" t="s">
+        <v>288</v>
+      </c>
+      <c r="D77" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" t="s">
+        <v>575</v>
+      </c>
+      <c r="F77" t="s">
+        <v>576</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>580</v>
+      </c>
+      <c r="B78" t="s">
+        <v>581</v>
+      </c>
+      <c r="C78" t="s">
+        <v>582</v>
+      </c>
+      <c r="D78" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" t="s">
+        <v>583</v>
+      </c>
+      <c r="F78" t="s">
+        <v>584</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>586</v>
+      </c>
+      <c r="B79" t="s">
+        <v>587</v>
+      </c>
+      <c r="C79" t="s">
+        <v>244</v>
+      </c>
+      <c r="D79" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" t="s">
+        <v>588</v>
+      </c>
+      <c r="F79" t="s">
+        <v>367</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>590</v>
+      </c>
+      <c r="B80" t="s">
+        <v>581</v>
+      </c>
+      <c r="C80" t="s">
+        <v>591</v>
+      </c>
+      <c r="D80" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" t="s">
+        <v>514</v>
+      </c>
+      <c r="F80" t="s">
+        <v>584</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>593</v>
+      </c>
+      <c r="B81" t="s">
+        <v>594</v>
+      </c>
+      <c r="C81" t="s">
+        <v>595</v>
+      </c>
+      <c r="D81" t="s">
+        <v>208</v>
+      </c>
+      <c r="E81" t="s">
+        <v>596</v>
+      </c>
+      <c r="F81" t="s">
+        <v>597</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>599</v>
+      </c>
+      <c r="B82" t="s">
+        <v>243</v>
+      </c>
+      <c r="C82" t="s">
+        <v>244</v>
+      </c>
+      <c r="D82" t="s">
+        <v>208</v>
+      </c>
+      <c r="E82" t="s">
+        <v>600</v>
+      </c>
+      <c r="F82" t="s">
+        <v>246</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>602</v>
+      </c>
+      <c r="B83" t="s">
+        <v>603</v>
+      </c>
+      <c r="C83" t="s">
+        <v>604</v>
+      </c>
+      <c r="D83" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" t="s">
+        <v>605</v>
+      </c>
+      <c r="F83" t="s">
+        <v>268</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>607</v>
+      </c>
+      <c r="B84" t="s">
+        <v>608</v>
+      </c>
+      <c r="C84" t="s">
+        <v>231</v>
+      </c>
+      <c r="D84" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" t="s">
+        <v>289</v>
+      </c>
+      <c r="F84" t="s">
+        <v>609</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>611</v>
+      </c>
+      <c r="B85" t="s">
+        <v>612</v>
+      </c>
+      <c r="C85" t="s">
+        <v>613</v>
+      </c>
+      <c r="D85" t="s">
+        <v>208</v>
+      </c>
+      <c r="E85" t="s">
+        <v>614</v>
+      </c>
+      <c r="F85" t="s">
+        <v>615</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>611</v>
+      </c>
+      <c r="B86" t="s">
+        <v>617</v>
+      </c>
+      <c r="C86" t="s">
+        <v>244</v>
+      </c>
+      <c r="D86" t="s">
+        <v>208</v>
+      </c>
+      <c r="E86" t="s">
+        <v>618</v>
+      </c>
+      <c r="F86" t="s">
+        <v>195</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>620</v>
+      </c>
+      <c r="B87" t="s">
+        <v>621</v>
+      </c>
+      <c r="C87" t="s">
+        <v>622</v>
+      </c>
+      <c r="D87" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" t="s">
+        <v>623</v>
+      </c>
+      <c r="F87" t="s">
+        <v>402</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>625</v>
+      </c>
+      <c r="B88" t="s">
+        <v>626</v>
+      </c>
+      <c r="C88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D88" t="s">
+        <v>232</v>
+      </c>
+      <c r="E88" t="s">
+        <v>628</v>
+      </c>
+      <c r="F88" t="s">
+        <v>629</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>631</v>
+      </c>
+      <c r="B89" t="s">
+        <v>626</v>
+      </c>
+      <c r="C89" t="s">
+        <v>627</v>
+      </c>
+      <c r="D89" t="s">
+        <v>232</v>
+      </c>
+      <c r="E89" t="s">
+        <v>258</v>
+      </c>
+      <c r="F89" t="s">
+        <v>407</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>633</v>
+      </c>
+      <c r="B90" t="s">
+        <v>634</v>
+      </c>
+      <c r="C90" t="s">
+        <v>635</v>
+      </c>
+      <c r="D90" t="s">
+        <v>208</v>
+      </c>
+      <c r="E90" t="s">
+        <v>636</v>
+      </c>
+      <c r="F90" t="s">
+        <v>637</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>633</v>
+      </c>
+      <c r="B91" t="s">
+        <v>639</v>
+      </c>
+      <c r="C91" t="s">
+        <v>640</v>
+      </c>
+      <c r="D91" t="s">
+        <v>208</v>
+      </c>
+      <c r="E91" t="s">
+        <v>641</v>
+      </c>
+      <c r="F91" t="s">
+        <v>642</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>644</v>
+      </c>
+      <c r="B92" t="s">
+        <v>399</v>
+      </c>
+      <c r="C92" t="s">
+        <v>400</v>
+      </c>
+      <c r="D92" t="s">
+        <v>208</v>
+      </c>
+      <c r="E92" t="s">
+        <v>645</v>
+      </c>
+      <c r="F92" t="s">
+        <v>402</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>647</v>
+      </c>
+      <c r="B93" t="s">
+        <v>621</v>
+      </c>
+      <c r="C93" t="s">
+        <v>622</v>
+      </c>
+      <c r="D93" t="s">
+        <v>208</v>
+      </c>
+      <c r="E93" t="s">
+        <v>648</v>
+      </c>
+      <c r="F93" t="s">
+        <v>402</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>650</v>
+      </c>
+      <c r="B94" t="s">
+        <v>651</v>
+      </c>
+      <c r="C94" t="s">
+        <v>200</v>
+      </c>
+      <c r="D94" t="s">
+        <v>208</v>
+      </c>
+      <c r="E94" t="s">
+        <v>262</v>
+      </c>
+      <c r="F94" t="s">
+        <v>652</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>654</v>
+      </c>
+      <c r="B95" t="s">
+        <v>639</v>
+      </c>
+      <c r="C95" t="s">
+        <v>640</v>
+      </c>
+      <c r="D95" t="s">
+        <v>208</v>
+      </c>
+      <c r="E95" t="s">
+        <v>655</v>
+      </c>
+      <c r="F95" t="s">
+        <v>656</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>658</v>
+      </c>
+      <c r="B96" t="s">
+        <v>659</v>
+      </c>
+      <c r="C96" t="s">
+        <v>660</v>
+      </c>
+      <c r="D96" t="s">
+        <v>208</v>
+      </c>
+      <c r="E96" t="s">
+        <v>661</v>
+      </c>
+      <c r="F96" t="s">
+        <v>662</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>664</v>
+      </c>
+      <c r="B97" t="s">
+        <v>332</v>
+      </c>
+      <c r="C97" t="s">
+        <v>333</v>
+      </c>
+      <c r="D97" t="s">
+        <v>251</v>
+      </c>
+      <c r="E97" t="s">
+        <v>665</v>
+      </c>
+      <c r="F97" t="s">
+        <v>666</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>668</v>
+      </c>
+      <c r="B98" t="s">
+        <v>669</v>
+      </c>
+      <c r="C98" t="s">
+        <v>244</v>
+      </c>
+      <c r="D98" t="s">
+        <v>208</v>
+      </c>
+      <c r="E98" t="s">
+        <v>670</v>
+      </c>
+      <c r="F98" t="s">
+        <v>671</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>673</v>
+      </c>
+      <c r="B99" t="s">
+        <v>674</v>
+      </c>
+      <c r="C99" t="s">
+        <v>675</v>
+      </c>
+      <c r="D99" t="s">
+        <v>232</v>
+      </c>
+      <c r="E99" t="s">
+        <v>676</v>
+      </c>
+      <c r="F99" t="s">
+        <v>677</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>679</v>
+      </c>
+      <c r="B100" t="s">
+        <v>680</v>
+      </c>
+      <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
+        <v>208</v>
+      </c>
+      <c r="E100" t="s">
+        <v>681</v>
+      </c>
+      <c r="F100" t="s">
+        <v>682</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>684</v>
+      </c>
+      <c r="B101" t="s">
+        <v>685</v>
+      </c>
+      <c r="C101" t="s">
+        <v>288</v>
+      </c>
+      <c r="D101" t="s">
+        <v>208</v>
+      </c>
+      <c r="E101" t="s">
+        <v>686</v>
+      </c>
+      <c r="F101" t="s">
+        <v>476</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>688</v>
+      </c>
+      <c r="B102" t="s">
+        <v>689</v>
+      </c>
+      <c r="C102" t="s">
+        <v>244</v>
+      </c>
+      <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
+        <v>690</v>
+      </c>
+      <c r="F102" t="s">
+        <v>341</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>692</v>
+      </c>
+      <c r="B103" t="s">
+        <v>693</v>
+      </c>
+      <c r="C103" t="s">
+        <v>694</v>
+      </c>
+      <c r="D103" t="s">
+        <v>569</v>
+      </c>
+      <c r="E103" t="s">
+        <v>695</v>
+      </c>
+      <c r="F103" t="s">
+        <v>696</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>698</v>
+      </c>
+      <c r="B104" t="s">
+        <v>699</v>
+      </c>
+      <c r="C104" t="s">
+        <v>700</v>
+      </c>
+      <c r="D104" t="s">
+        <v>208</v>
+      </c>
+      <c r="E104" t="s">
+        <v>701</v>
+      </c>
+      <c r="F104" t="s">
+        <v>702</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>698</v>
+      </c>
+      <c r="B105" t="s">
+        <v>699</v>
+      </c>
+      <c r="C105" t="s">
+        <v>582</v>
+      </c>
+      <c r="D105" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" t="s">
+        <v>701</v>
+      </c>
+      <c r="F105" t="s">
+        <v>702</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>698</v>
+      </c>
+      <c r="B106" t="s">
+        <v>699</v>
+      </c>
+      <c r="C106" t="s">
+        <v>705</v>
+      </c>
+      <c r="D106" t="s">
+        <v>208</v>
+      </c>
+      <c r="E106" t="s">
+        <v>701</v>
+      </c>
+      <c r="F106" t="s">
+        <v>702</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>698</v>
+      </c>
+      <c r="B107" t="s">
+        <v>699</v>
+      </c>
+      <c r="C107" t="s">
+        <v>640</v>
+      </c>
+      <c r="D107" t="s">
+        <v>208</v>
+      </c>
+      <c r="E107" t="s">
+        <v>701</v>
+      </c>
+      <c r="F107" t="s">
+        <v>702</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>698</v>
+      </c>
+      <c r="B108" t="s">
+        <v>699</v>
+      </c>
+      <c r="C108" t="s">
+        <v>708</v>
+      </c>
+      <c r="D108" t="s">
+        <v>208</v>
+      </c>
+      <c r="E108" t="s">
+        <v>701</v>
+      </c>
+      <c r="F108" t="s">
+        <v>702</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -2474,6 +5940,97 @@
     <hyperlink ref="H15" r:id="rId14"/>
     <hyperlink ref="H16" r:id="rId15"/>
     <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-21.xlsx
+++ b/docs/xlsx/jobs-2026-08-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="718">
   <si>
     <t>Title</t>
   </si>
@@ -1282,6 +1282,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc5506be669f40f5abcdc61e44a6266b-executive-director-las-vegas-new-mexico-community-foundation-las-vegas</t>
   </si>
   <si>
+    <t>Earth Matter NY Inc.</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9eb911f5213c4d7d857f497103efe8f4-executive-director-earth-matter-ny-inc-new-york</t>
+  </si>
+  <si>
     <t>Executive Director Cake4Kids</t>
   </si>
   <si>
@@ -1630,6 +1642,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b0e1982cb3a49d8beba600b6dc1bb50-operations-coordinator-kinship-house-portland</t>
   </si>
   <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>Housing Leadership Council of San Mateo County</t>
+  </si>
+  <si>
+    <t>San Mateo, CA</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/844d2dd1185740d4b82c89459e1b2485-organizer-housing-leadership-council-of-san-mateo-county-san-mateo</t>
+  </si>
+  <si>
     <t>Outpatient Clinician/ Therapist</t>
   </si>
   <si>
@@ -1639,9 +1669,6 @@
     <t>Chula Vista, California</t>
   </si>
   <si>
-    <t>USD 68000.00 - 75000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Family, Mental Health</t>
   </si>
   <si>
@@ -1742,9 +1769,6 @@
   </si>
   <si>
     <t>USD 32.69 - 34.13/hour</t>
-  </si>
-  <si>
-    <t>Civic Engagement, Community Development, Economic Development</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/cb4a4aa6590b4c069082a3acb314342c-prison-and-reentry-program-manager-defy-ventures-seattle</t>
@@ -3421,7 +3445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4451,171 +4475,171 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
         <v>422</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" t="s">
         <v>423</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>424</v>
       </c>
-      <c r="D45" t="s">
-        <v>208</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="H45" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="F45" t="s">
-        <v>426</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>426</v>
+      </c>
+      <c r="B46" t="s">
+        <v>427</v>
+      </c>
+      <c r="C46" t="s">
         <v>428</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" t="s">
         <v>429</v>
       </c>
-      <c r="C46" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" t="s">
-        <v>208</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>430</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>432</v>
+      </c>
+      <c r="B47" t="s">
         <v>433</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>200</v>
+      </c>
+      <c r="D47" t="s">
+        <v>208</v>
+      </c>
+      <c r="E47" t="s">
         <v>434</v>
       </c>
-      <c r="C47" t="s">
+      <c r="F47" t="s">
         <v>435</v>
       </c>
-      <c r="D47" t="s">
-        <v>208</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="H47" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="F47" t="s">
-        <v>437</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>437</v>
+      </c>
+      <c r="B48" t="s">
+        <v>438</v>
+      </c>
+      <c r="C48" t="s">
         <v>439</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
+        <v>208</v>
+      </c>
+      <c r="E48" t="s">
         <v>440</v>
       </c>
-      <c r="C48" t="s">
-        <v>244</v>
-      </c>
-      <c r="D48" t="s">
-        <v>208</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>441</v>
       </c>
-      <c r="F48" t="s">
+      <c r="H48" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>443</v>
+      </c>
+      <c r="B49" t="s">
         <v>444</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" t="s">
+        <v>208</v>
+      </c>
+      <c r="E49" t="s">
         <v>445</v>
       </c>
-      <c r="C49" t="s">
-        <v>231</v>
-      </c>
-      <c r="D49" t="s">
-        <v>251</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>446</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>448</v>
+      </c>
+      <c r="B50" t="s">
         <v>449</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" t="s">
         <v>450</v>
       </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
         <v>451</v>
       </c>
-      <c r="D50" t="s">
-        <v>208</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="H50" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="F50" t="s">
-        <v>453</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>453</v>
+      </c>
+      <c r="B51" t="s">
+        <v>454</v>
+      </c>
+      <c r="C51" t="s">
         <v>455</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E51" t="s">
         <v>456</v>
       </c>
-      <c r="C51" t="s">
+      <c r="F51" t="s">
         <v>457</v>
       </c>
-      <c r="D51" t="s">
-        <v>208</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="H51" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="F51" t="s">
-        <v>459</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C52" t="s">
         <v>461</v>
@@ -4624,21 +4648,21 @@
         <v>208</v>
       </c>
       <c r="E52" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F52" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B53" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C53" t="s">
         <v>465</v>
@@ -4647,33 +4671,33 @@
         <v>208</v>
       </c>
       <c r="E53" t="s">
+        <v>462</v>
+      </c>
+      <c r="F53" t="s">
+        <v>463</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="F53" t="s">
-        <v>467</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>467</v>
+      </c>
+      <c r="B54" t="s">
+        <v>468</v>
+      </c>
+      <c r="C54" t="s">
         <v>469</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
+        <v>208</v>
+      </c>
+      <c r="E54" t="s">
         <v>470</v>
       </c>
-      <c r="C54" t="s">
-        <v>231</v>
-      </c>
-      <c r="D54" t="s">
-        <v>208</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>471</v>
-      </c>
-      <c r="F54" t="s">
-        <v>341</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>472</v>
@@ -4687,7 +4711,7 @@
         <v>474</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>231</v>
       </c>
       <c r="D55" t="s">
         <v>208</v>
@@ -4696,53 +4720,53 @@
         <v>475</v>
       </c>
       <c r="F55" t="s">
+        <v>341</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>477</v>
+      </c>
+      <c r="B56" t="s">
         <v>478</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>323</v>
+      </c>
+      <c r="D56" t="s">
+        <v>208</v>
+      </c>
+      <c r="E56" t="s">
         <v>479</v>
       </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
         <v>480</v>
       </c>
-      <c r="D56" t="s">
-        <v>208</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="H56" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="F56" t="s">
-        <v>482</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>482</v>
+      </c>
+      <c r="B57" t="s">
+        <v>483</v>
+      </c>
+      <c r="C57" t="s">
         <v>484</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
+        <v>208</v>
+      </c>
+      <c r="E57" t="s">
         <v>485</v>
       </c>
-      <c r="C57" t="s">
-        <v>200</v>
-      </c>
-      <c r="D57" t="s">
-        <v>208</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>486</v>
-      </c>
-      <c r="F57" t="s">
-        <v>195</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>487</v>
@@ -4756,7 +4780,7 @@
         <v>489</v>
       </c>
       <c r="C58" t="s">
-        <v>323</v>
+        <v>200</v>
       </c>
       <c r="D58" t="s">
         <v>208</v>
@@ -4765,44 +4789,44 @@
         <v>490</v>
       </c>
       <c r="F58" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>492</v>
+      </c>
+      <c r="B59" t="s">
         <v>493</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
+        <v>323</v>
+      </c>
+      <c r="D59" t="s">
+        <v>208</v>
+      </c>
+      <c r="E59" t="s">
         <v>494</v>
       </c>
-      <c r="C59" t="s">
+      <c r="F59" t="s">
         <v>495</v>
       </c>
-      <c r="D59" t="s">
-        <v>208</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="H59" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="F59" t="s">
-        <v>497</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>497</v>
+      </c>
+      <c r="B60" t="s">
+        <v>498</v>
+      </c>
+      <c r="C60" t="s">
         <v>499</v>
-      </c>
-      <c r="B60" t="s">
-        <v>479</v>
-      </c>
-      <c r="C60" t="s">
-        <v>480</v>
       </c>
       <c r="D60" t="s">
         <v>208</v>
@@ -4811,67 +4835,67 @@
         <v>500</v>
       </c>
       <c r="F60" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B61" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="C61" t="s">
+        <v>484</v>
+      </c>
+      <c r="D61" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" t="s">
         <v>504</v>
       </c>
-      <c r="D61" t="s">
-        <v>208</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
+        <v>486</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="F61" t="s">
-        <v>506</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>506</v>
+      </c>
+      <c r="B62" t="s">
+        <v>507</v>
+      </c>
+      <c r="C62" t="s">
         <v>508</v>
       </c>
-      <c r="B62" t="s">
+      <c r="D62" t="s">
+        <v>208</v>
+      </c>
+      <c r="E62" t="s">
         <v>509</v>
       </c>
-      <c r="C62" t="s">
-        <v>231</v>
-      </c>
-      <c r="D62" t="s">
-        <v>208</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>510</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>512</v>
+      </c>
+      <c r="B63" t="s">
         <v>513</v>
       </c>
-      <c r="B63" t="s">
-        <v>243</v>
-      </c>
       <c r="C63" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
         <v>208</v>
@@ -4891,108 +4915,108 @@
         <v>517</v>
       </c>
       <c r="B64" t="s">
+        <v>243</v>
+      </c>
+      <c r="C64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" t="s">
         <v>518</v>
       </c>
-      <c r="C64" t="s">
-        <v>413</v>
-      </c>
-      <c r="D64" t="s">
-        <v>208</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>519</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>521</v>
+      </c>
+      <c r="B65" t="s">
         <v>522</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>413</v>
+      </c>
+      <c r="D65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" t="s">
         <v>523</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>524</v>
       </c>
-      <c r="D65" t="s">
-        <v>208</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="H65" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="F65" t="s">
-        <v>195</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>526</v>
+      </c>
+      <c r="B66" t="s">
         <v>527</v>
       </c>
-      <c r="B66" t="s">
-        <v>338</v>
-      </c>
       <c r="C66" t="s">
-        <v>219</v>
+        <v>528</v>
       </c>
       <c r="D66" t="s">
         <v>208</v>
       </c>
       <c r="E66" t="s">
-        <v>340</v>
+        <v>529</v>
       </c>
       <c r="F66" t="s">
-        <v>341</v>
+        <v>195</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B67" t="s">
-        <v>530</v>
+        <v>338</v>
       </c>
       <c r="C67" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="D67" t="s">
         <v>208</v>
       </c>
       <c r="E67" t="s">
-        <v>531</v>
+        <v>340</v>
       </c>
       <c r="F67" t="s">
+        <v>341</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>533</v>
+      </c>
+      <c r="B68" t="s">
         <v>534</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>244</v>
+      </c>
+      <c r="D68" t="s">
+        <v>208</v>
+      </c>
+      <c r="E68" t="s">
         <v>535</v>
-      </c>
-      <c r="C68" t="s">
-        <v>374</v>
-      </c>
-      <c r="D68" t="s">
-        <v>208</v>
-      </c>
-      <c r="E68" t="s">
-        <v>380</v>
       </c>
       <c r="F68" t="s">
         <v>536</v>
@@ -5009,39 +5033,39 @@
         <v>539</v>
       </c>
       <c r="C69" t="s">
+        <v>374</v>
+      </c>
+      <c r="D69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E69" t="s">
+        <v>380</v>
+      </c>
+      <c r="F69" t="s">
         <v>540</v>
       </c>
-      <c r="D69" t="s">
-        <v>208</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="H69" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="F69" t="s">
-        <v>542</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>542</v>
+      </c>
+      <c r="B70" t="s">
+        <v>543</v>
+      </c>
+      <c r="C70" t="s">
         <v>544</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
+        <v>208</v>
+      </c>
+      <c r="E70" t="s">
         <v>545</v>
       </c>
-      <c r="C70" t="s">
-        <v>244</v>
-      </c>
-      <c r="D70" t="s">
-        <v>208</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>546</v>
-      </c>
-      <c r="F70" t="s">
-        <v>402</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>547</v>
@@ -5052,42 +5076,42 @@
         <v>548</v>
       </c>
       <c r="B71" t="s">
-        <v>304</v>
+        <v>549</v>
       </c>
       <c r="C71" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D71" t="s">
         <v>208</v>
       </c>
       <c r="E71" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="F71" t="s">
-        <v>307</v>
+        <v>551</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B72" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C72" t="s">
-        <v>413</v>
+        <v>244</v>
       </c>
       <c r="D72" t="s">
         <v>208</v>
       </c>
       <c r="E72" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F72" t="s">
-        <v>555</v>
+        <v>402</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>556</v>
@@ -5098,10 +5122,10 @@
         <v>557</v>
       </c>
       <c r="B73" t="s">
+        <v>304</v>
+      </c>
+      <c r="C73" t="s">
         <v>558</v>
-      </c>
-      <c r="C73" t="s">
-        <v>244</v>
       </c>
       <c r="D73" t="s">
         <v>208</v>
@@ -5110,18 +5134,18 @@
         <v>559</v>
       </c>
       <c r="F73" t="s">
+        <v>307</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>561</v>
+      </c>
+      <c r="B74" t="s">
         <v>562</v>
-      </c>
-      <c r="B74" t="s">
-        <v>563</v>
       </c>
       <c r="C74" t="s">
         <v>413</v>
@@ -5130,102 +5154,102 @@
         <v>208</v>
       </c>
       <c r="E74" t="s">
+        <v>563</v>
+      </c>
+      <c r="F74" t="s">
         <v>564</v>
       </c>
-      <c r="F74" t="s">
+      <c r="H74" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>566</v>
+      </c>
+      <c r="B75" t="s">
         <v>567</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" t="s">
         <v>568</v>
       </c>
-      <c r="C75" t="s">
-        <v>400</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
         <v>569</v>
       </c>
-      <c r="E75" t="s">
+      <c r="H75" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="F75" t="s">
-        <v>571</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>571</v>
+      </c>
+      <c r="B76" t="s">
+        <v>572</v>
+      </c>
+      <c r="C76" t="s">
+        <v>413</v>
+      </c>
+      <c r="D76" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" t="s">
         <v>573</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
         <v>574</v>
       </c>
-      <c r="C76" t="s">
-        <v>288</v>
-      </c>
-      <c r="D76" t="s">
-        <v>208</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="H76" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="F76" t="s">
-        <v>576</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>576</v>
+      </c>
+      <c r="B77" t="s">
+        <v>577</v>
+      </c>
+      <c r="C77" t="s">
+        <v>400</v>
+      </c>
+      <c r="D77" t="s">
         <v>578</v>
       </c>
-      <c r="B77" t="s">
-        <v>574</v>
-      </c>
-      <c r="C77" t="s">
-        <v>288</v>
-      </c>
-      <c r="D77" t="s">
-        <v>208</v>
-      </c>
       <c r="E77" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F77" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B78" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C78" t="s">
-        <v>582</v>
+        <v>288</v>
       </c>
       <c r="D78" t="s">
         <v>208</v>
       </c>
       <c r="E78" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F78" t="s">
-        <v>584</v>
+        <v>546</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>585</v>
@@ -5236,56 +5260,56 @@
         <v>586</v>
       </c>
       <c r="B79" t="s">
+        <v>583</v>
+      </c>
+      <c r="C79" t="s">
+        <v>288</v>
+      </c>
+      <c r="D79" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" t="s">
+        <v>584</v>
+      </c>
+      <c r="F79" t="s">
+        <v>546</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="C79" t="s">
-        <v>244</v>
-      </c>
-      <c r="D79" t="s">
-        <v>208</v>
-      </c>
-      <c r="E79" t="s">
-        <v>588</v>
-      </c>
-      <c r="F79" t="s">
-        <v>367</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>588</v>
+      </c>
+      <c r="B80" t="s">
+        <v>589</v>
+      </c>
+      <c r="C80" t="s">
         <v>590</v>
       </c>
-      <c r="B80" t="s">
-        <v>581</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" t="s">
         <v>591</v>
       </c>
-      <c r="D80" t="s">
-        <v>208</v>
-      </c>
-      <c r="E80" t="s">
-        <v>514</v>
-      </c>
       <c r="F80" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B81" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C81" t="s">
-        <v>595</v>
+        <v>244</v>
       </c>
       <c r="D81" t="s">
         <v>208</v>
@@ -5294,53 +5318,53 @@
         <v>596</v>
       </c>
       <c r="F81" t="s">
+        <v>367</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>598</v>
+      </c>
+      <c r="B82" t="s">
+        <v>589</v>
+      </c>
+      <c r="C82" t="s">
         <v>599</v>
       </c>
-      <c r="B82" t="s">
-        <v>243</v>
-      </c>
-      <c r="C82" t="s">
-        <v>244</v>
-      </c>
       <c r="D82" t="s">
         <v>208</v>
       </c>
       <c r="E82" t="s">
+        <v>518</v>
+      </c>
+      <c r="F82" t="s">
+        <v>592</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="F82" t="s">
-        <v>246</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>601</v>
+      </c>
+      <c r="B83" t="s">
         <v>602</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>603</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" t="s">
         <v>604</v>
       </c>
-      <c r="D83" t="s">
-        <v>208</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>605</v>
-      </c>
-      <c r="F83" t="s">
-        <v>268</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>606</v>
@@ -5351,88 +5375,88 @@
         <v>607</v>
       </c>
       <c r="B84" t="s">
+        <v>243</v>
+      </c>
+      <c r="C84" t="s">
+        <v>244</v>
+      </c>
+      <c r="D84" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" t="s">
         <v>608</v>
       </c>
-      <c r="C84" t="s">
-        <v>231</v>
-      </c>
-      <c r="D84" t="s">
-        <v>208</v>
-      </c>
-      <c r="E84" t="s">
-        <v>289</v>
-      </c>
       <c r="F84" t="s">
+        <v>246</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>610</v>
+      </c>
+      <c r="B85" t="s">
         <v>611</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>612</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>208</v>
+      </c>
+      <c r="E85" t="s">
         <v>613</v>
       </c>
-      <c r="D85" t="s">
-        <v>208</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>268</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="F85" t="s">
-        <v>615</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B86" t="s">
+        <v>616</v>
+      </c>
+      <c r="C86" t="s">
+        <v>231</v>
+      </c>
+      <c r="D86" t="s">
+        <v>208</v>
+      </c>
+      <c r="E86" t="s">
+        <v>289</v>
+      </c>
+      <c r="F86" t="s">
         <v>617</v>
       </c>
-      <c r="C86" t="s">
-        <v>244</v>
-      </c>
-      <c r="D86" t="s">
-        <v>208</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="H86" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="F86" t="s">
-        <v>195</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>619</v>
+      </c>
+      <c r="B87" t="s">
         <v>620</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>621</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" t="s">
         <v>622</v>
       </c>
-      <c r="D87" t="s">
-        <v>208</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>623</v>
-      </c>
-      <c r="F87" t="s">
-        <v>402</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>624</v>
@@ -5440,45 +5464,45 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>619</v>
+      </c>
+      <c r="B88" t="s">
         <v>625</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>244</v>
+      </c>
+      <c r="D88" t="s">
+        <v>208</v>
+      </c>
+      <c r="E88" t="s">
         <v>626</v>
       </c>
-      <c r="C88" t="s">
+      <c r="F88" t="s">
+        <v>195</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D88" t="s">
-        <v>232</v>
-      </c>
-      <c r="E88" t="s">
-        <v>628</v>
-      </c>
-      <c r="F88" t="s">
-        <v>629</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>628</v>
+      </c>
+      <c r="B89" t="s">
+        <v>629</v>
+      </c>
+      <c r="C89" t="s">
+        <v>630</v>
+      </c>
+      <c r="D89" t="s">
+        <v>208</v>
+      </c>
+      <c r="E89" t="s">
         <v>631</v>
       </c>
-      <c r="B89" t="s">
-        <v>626</v>
-      </c>
-      <c r="C89" t="s">
-        <v>627</v>
-      </c>
-      <c r="D89" t="s">
-        <v>232</v>
-      </c>
-      <c r="E89" t="s">
-        <v>258</v>
-      </c>
       <c r="F89" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>632</v>
@@ -5495,7 +5519,7 @@
         <v>635</v>
       </c>
       <c r="D90" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="E90" t="s">
         <v>636</v>
@@ -5509,45 +5533,45 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B91" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C91" t="s">
+        <v>635</v>
+      </c>
+      <c r="D91" t="s">
+        <v>232</v>
+      </c>
+      <c r="E91" t="s">
+        <v>258</v>
+      </c>
+      <c r="F91" t="s">
+        <v>407</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="D91" t="s">
-        <v>208</v>
-      </c>
-      <c r="E91" t="s">
-        <v>641</v>
-      </c>
-      <c r="F91" t="s">
-        <v>642</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>641</v>
+      </c>
+      <c r="B92" t="s">
+        <v>642</v>
+      </c>
+      <c r="C92" t="s">
+        <v>643</v>
+      </c>
+      <c r="D92" t="s">
+        <v>208</v>
+      </c>
+      <c r="E92" t="s">
         <v>644</v>
       </c>
-      <c r="B92" t="s">
-        <v>399</v>
-      </c>
-      <c r="C92" t="s">
-        <v>400</v>
-      </c>
-      <c r="D92" t="s">
-        <v>208</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>645</v>
-      </c>
-      <c r="F92" t="s">
-        <v>402</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>646</v>
@@ -5555,68 +5579,68 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>641</v>
+      </c>
+      <c r="B93" t="s">
         <v>647</v>
       </c>
-      <c r="B93" t="s">
-        <v>621</v>
-      </c>
       <c r="C93" t="s">
-        <v>622</v>
+        <v>648</v>
       </c>
       <c r="D93" t="s">
         <v>208</v>
       </c>
       <c r="E93" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F93" t="s">
-        <v>402</v>
+        <v>650</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B94" t="s">
-        <v>651</v>
+        <v>399</v>
       </c>
       <c r="C94" t="s">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D94" t="s">
         <v>208</v>
       </c>
       <c r="E94" t="s">
-        <v>262</v>
+        <v>653</v>
       </c>
       <c r="F94" t="s">
-        <v>652</v>
+        <v>402</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B95" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C95" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="D95" t="s">
         <v>208</v>
       </c>
       <c r="E95" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F95" t="s">
-        <v>656</v>
+        <v>402</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>657</v>
@@ -5630,154 +5654,154 @@
         <v>659</v>
       </c>
       <c r="C96" t="s">
+        <v>200</v>
+      </c>
+      <c r="D96" t="s">
+        <v>208</v>
+      </c>
+      <c r="E96" t="s">
+        <v>262</v>
+      </c>
+      <c r="F96" t="s">
         <v>660</v>
       </c>
-      <c r="D96" t="s">
-        <v>208</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="H96" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="F96" t="s">
-        <v>662</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>662</v>
+      </c>
+      <c r="B97" t="s">
+        <v>647</v>
+      </c>
+      <c r="C97" t="s">
+        <v>648</v>
+      </c>
+      <c r="D97" t="s">
+        <v>208</v>
+      </c>
+      <c r="E97" t="s">
+        <v>663</v>
+      </c>
+      <c r="F97" t="s">
         <v>664</v>
       </c>
-      <c r="B97" t="s">
-        <v>332</v>
-      </c>
-      <c r="C97" t="s">
-        <v>333</v>
-      </c>
-      <c r="D97" t="s">
-        <v>251</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="H97" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="F97" t="s">
-        <v>666</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>666</v>
+      </c>
+      <c r="B98" t="s">
+        <v>667</v>
+      </c>
+      <c r="C98" t="s">
         <v>668</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
+        <v>208</v>
+      </c>
+      <c r="E98" t="s">
         <v>669</v>
       </c>
-      <c r="C98" t="s">
-        <v>244</v>
-      </c>
-      <c r="D98" t="s">
-        <v>208</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>670</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>672</v>
+      </c>
+      <c r="B99" t="s">
+        <v>332</v>
+      </c>
+      <c r="C99" t="s">
+        <v>333</v>
+      </c>
+      <c r="D99" t="s">
+        <v>251</v>
+      </c>
+      <c r="E99" t="s">
         <v>673</v>
       </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
         <v>674</v>
       </c>
-      <c r="C99" t="s">
+      <c r="H99" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D99" t="s">
-        <v>232</v>
-      </c>
-      <c r="E99" t="s">
-        <v>676</v>
-      </c>
-      <c r="F99" t="s">
-        <v>677</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>676</v>
+      </c>
+      <c r="B100" t="s">
+        <v>677</v>
+      </c>
+      <c r="C100" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" t="s">
+        <v>208</v>
+      </c>
+      <c r="E100" t="s">
+        <v>678</v>
+      </c>
+      <c r="F100" t="s">
         <v>679</v>
       </c>
-      <c r="B100" t="s">
+      <c r="H100" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C100" t="s">
-        <v>238</v>
-      </c>
-      <c r="D100" t="s">
-        <v>208</v>
-      </c>
-      <c r="E100" t="s">
-        <v>681</v>
-      </c>
-      <c r="F100" t="s">
-        <v>682</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>681</v>
+      </c>
+      <c r="B101" t="s">
+        <v>682</v>
+      </c>
+      <c r="C101" t="s">
+        <v>683</v>
+      </c>
+      <c r="D101" t="s">
+        <v>232</v>
+      </c>
+      <c r="E101" t="s">
         <v>684</v>
       </c>
-      <c r="B101" t="s">
+      <c r="F101" t="s">
         <v>685</v>
       </c>
-      <c r="C101" t="s">
-        <v>288</v>
-      </c>
-      <c r="D101" t="s">
-        <v>208</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="H101" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="F101" t="s">
-        <v>476</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>687</v>
+      </c>
+      <c r="B102" t="s">
         <v>688</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
+        <v>238</v>
+      </c>
+      <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
         <v>689</v>
       </c>
-      <c r="C102" t="s">
-        <v>244</v>
-      </c>
-      <c r="D102" t="s">
-        <v>208</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>690</v>
-      </c>
-      <c r="F102" t="s">
-        <v>341</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>691</v>
@@ -5791,134 +5815,180 @@
         <v>693</v>
       </c>
       <c r="C103" t="s">
+        <v>288</v>
+      </c>
+      <c r="D103" t="s">
+        <v>208</v>
+      </c>
+      <c r="E103" t="s">
         <v>694</v>
       </c>
-      <c r="D103" t="s">
-        <v>569</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>480</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="F103" t="s">
-        <v>696</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>696</v>
+      </c>
+      <c r="B104" t="s">
+        <v>697</v>
+      </c>
+      <c r="C104" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" t="s">
+        <v>208</v>
+      </c>
+      <c r="E104" t="s">
         <v>698</v>
       </c>
-      <c r="B104" t="s">
+      <c r="F104" t="s">
+        <v>341</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="C104" t="s">
-        <v>700</v>
-      </c>
-      <c r="D104" t="s">
-        <v>208</v>
-      </c>
-      <c r="E104" t="s">
-        <v>701</v>
-      </c>
-      <c r="F104" t="s">
-        <v>702</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B105" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C105" t="s">
-        <v>582</v>
+        <v>702</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>578</v>
       </c>
       <c r="E105" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="F105" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B106" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C106" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D106" t="s">
         <v>208</v>
       </c>
       <c r="E106" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="F106" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B107" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C107" t="s">
-        <v>640</v>
+        <v>590</v>
       </c>
       <c r="D107" t="s">
         <v>208</v>
       </c>
       <c r="E107" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="F107" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B108" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C108" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="D108" t="s">
         <v>208</v>
       </c>
       <c r="E108" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="F108" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="H108" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>706</v>
+      </c>
+      <c r="B109" t="s">
+        <v>707</v>
+      </c>
+      <c r="C109" t="s">
+        <v>648</v>
+      </c>
+      <c r="D109" t="s">
+        <v>208</v>
+      </c>
+      <c r="E109" t="s">
         <v>709</v>
+      </c>
+      <c r="F109" t="s">
+        <v>710</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>706</v>
+      </c>
+      <c r="B110" t="s">
+        <v>707</v>
+      </c>
+      <c r="C110" t="s">
+        <v>716</v>
+      </c>
+      <c r="D110" t="s">
+        <v>208</v>
+      </c>
+      <c r="E110" t="s">
+        <v>709</v>
+      </c>
+      <c r="F110" t="s">
+        <v>710</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -6031,6 +6101,8 @@
     <hyperlink ref="H106" r:id="rId105"/>
     <hyperlink ref="H107" r:id="rId106"/>
     <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
